--- a/plan/pubgen/samples/DUAL_LANG/BAB_01_2025_no_div_ai_translate.xlsx
+++ b/plan/pubgen/samples/DUAL_LANG/BAB_01_2025_no_div_ai_translate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\designcraft\plan\pubgen\samples\DUAL_LANG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\designcraft-pubgen-0.7.X\plan\pubgen\samples\DUAL_LANG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADADA85D-B4A7-4FA6-A33B-1B8AE4EDB97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43307D0-80DA-4791-A317-C6E8413D2D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="2505" windowWidth="28800" windowHeight="9720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER" sheetId="7" r:id="rId1"/>
@@ -21,18 +21,21 @@
     <sheet name="G02" sheetId="12" r:id="rId6"/>
     <sheet name="R01" sheetId="14" r:id="rId7"/>
     <sheet name="01_01" sheetId="13" r:id="rId8"/>
-    <sheet name="note" sheetId="8" r:id="rId9"/>
+    <sheet name="03_02" sheetId="16" r:id="rId9"/>
+    <sheet name="note" sheetId="8" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_Toc202275224" localSheetId="7">'01_01'!#REF!</definedName>
     <definedName name="_Toc202275225" localSheetId="7">'01_01'!#REF!</definedName>
+    <definedName name="_Toc234494054" localSheetId="8">'03_02'!$B$1</definedName>
+    <definedName name="_Toc234494055" localSheetId="8">'03_02'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="100">
   <si>
     <t>Warungbambu</t>
   </si>
@@ -276,12 +279,84 @@
   <si>
     <t>Kec. Karawang Timur</t>
   </si>
+  <si>
+    <t>Kelompok Umur</t>
+  </si>
+  <si>
+    <t>Laki-Laki</t>
+  </si>
+  <si>
+    <t>Perempuan</t>
+  </si>
+  <si>
+    <t>Jumlah</t>
+  </si>
+  <si>
+    <t>00-04</t>
+  </si>
+  <si>
+    <t>15-19</t>
+  </si>
+  <si>
+    <t>20-24</t>
+  </si>
+  <si>
+    <t>25-29</t>
+  </si>
+  <si>
+    <t>30-34</t>
+  </si>
+  <si>
+    <t>35-39</t>
+  </si>
+  <si>
+    <t>40-44</t>
+  </si>
+  <si>
+    <t>45-49</t>
+  </si>
+  <si>
+    <t>50-54</t>
+  </si>
+  <si>
+    <t>55-59</t>
+  </si>
+  <si>
+    <t>60-64</t>
+  </si>
+  <si>
+    <t>65-69</t>
+  </si>
+  <si>
+    <t>70-74</t>
+  </si>
+  <si>
+    <t>75+</t>
+  </si>
+  <si>
+    <t>Tabel 03.02 Jumlah Penduduk Menurut Kelompok Umur dan Jenis Kelamin di Kecamatan Karawang Timur, 2025</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>BPS Kabupaten Karawang</t>
+  </si>
+  <si>
+    <t>Jenis Kelamin</t>
+  </si>
+  <si>
+    <t>05-09</t>
+  </si>
+  <si>
+    <t>10-14</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -324,6 +399,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -345,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
@@ -378,6 +478,36 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -805,6 +935,83 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FF3748-2C15-42F2-916C-09F0CB4E6713}">
+  <dimension ref="N1:O11"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="14" max="14" width="23.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="14:15" x14ac:dyDescent="0.2">
+      <c r="N1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="14:15" x14ac:dyDescent="0.2">
+      <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="14:15" x14ac:dyDescent="0.2">
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="14:15" x14ac:dyDescent="0.2">
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="14:15" x14ac:dyDescent="0.2">
+      <c r="N5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="14:15" x14ac:dyDescent="0.2">
+      <c r="N6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="14:15" x14ac:dyDescent="0.2">
+      <c r="N7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="14:15" x14ac:dyDescent="0.2">
+      <c r="N8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="14:15" x14ac:dyDescent="0.2">
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="14:15" x14ac:dyDescent="0.2">
+      <c r="N10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="14:15" x14ac:dyDescent="0.2">
+      <c r="N11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2506FEBA-5514-4FB9-BFCF-B90FF466BBEF}">
   <dimension ref="A1:B1"/>
@@ -1177,78 +1384,331 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FF3748-2C15-42F2-916C-09F0CB4E6713}">
-  <dimension ref="N1:O11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDBD8E32-D4D5-4C73-8695-952828F1A118}">
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="14" max="14" width="23.5703125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="14:15" x14ac:dyDescent="0.2">
-      <c r="N1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="14:15" x14ac:dyDescent="0.2">
-      <c r="N2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="14:15" x14ac:dyDescent="0.2">
-      <c r="N3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="14:15" x14ac:dyDescent="0.2">
-      <c r="N4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="14:15" x14ac:dyDescent="0.2">
-      <c r="N5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="14:15" x14ac:dyDescent="0.2">
-      <c r="N6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="14:15" x14ac:dyDescent="0.2">
-      <c r="N7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="14:15" x14ac:dyDescent="0.2">
-      <c r="N8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="14:15" x14ac:dyDescent="0.2">
-      <c r="N9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="14:15" x14ac:dyDescent="0.2">
-      <c r="N10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="14:15" x14ac:dyDescent="0.2">
-      <c r="N11" t="s">
-        <v>27</v>
-      </c>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="19"/>
+      <c r="B3" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="21">
+        <v>6842</v>
+      </c>
+      <c r="C4" s="21">
+        <v>5983</v>
+      </c>
+      <c r="D4" s="21">
+        <v>12825</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="21">
+        <v>7940</v>
+      </c>
+      <c r="C5" s="21">
+        <v>7742</v>
+      </c>
+      <c r="D5" s="21">
+        <v>15682</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="21">
+        <v>7642</v>
+      </c>
+      <c r="C6" s="21">
+        <v>6941</v>
+      </c>
+      <c r="D6" s="21">
+        <v>14583</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="21">
+        <v>3891</v>
+      </c>
+      <c r="C7" s="21">
+        <v>2853</v>
+      </c>
+      <c r="D7" s="21">
+        <v>6744</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="21">
+        <v>5844</v>
+      </c>
+      <c r="C8" s="21">
+        <v>4948</v>
+      </c>
+      <c r="D8" s="21">
+        <v>10792</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="21">
+        <v>6021</v>
+      </c>
+      <c r="C9" s="21">
+        <v>4973</v>
+      </c>
+      <c r="D9" s="21">
+        <v>10994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="21">
+        <v>6972</v>
+      </c>
+      <c r="C10" s="21">
+        <v>5942</v>
+      </c>
+      <c r="D10" s="21">
+        <v>12914</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="21">
+        <v>5931</v>
+      </c>
+      <c r="C11" s="21">
+        <v>5844</v>
+      </c>
+      <c r="D11" s="21">
+        <v>11775</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="21">
+        <v>6077</v>
+      </c>
+      <c r="C12" s="21">
+        <v>6188</v>
+      </c>
+      <c r="D12" s="21">
+        <v>12265</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="21">
+        <v>4681</v>
+      </c>
+      <c r="C13" s="21">
+        <v>4972</v>
+      </c>
+      <c r="D13" s="21">
+        <v>9653</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="21">
+        <v>3482</v>
+      </c>
+      <c r="C14" s="21">
+        <v>3987</v>
+      </c>
+      <c r="D14" s="21">
+        <v>7469</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="21">
+        <v>2160</v>
+      </c>
+      <c r="C15" s="21">
+        <v>2569</v>
+      </c>
+      <c r="D15" s="21">
+        <v>4729</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="21">
+        <v>1538</v>
+      </c>
+      <c r="C16" s="21">
+        <v>1480</v>
+      </c>
+      <c r="D16" s="21">
+        <v>3018</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="21">
+        <v>1239</v>
+      </c>
+      <c r="C17" s="21">
+        <v>1484</v>
+      </c>
+      <c r="D17" s="21">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="21">
+        <v>831</v>
+      </c>
+      <c r="C18" s="21">
+        <v>826</v>
+      </c>
+      <c r="D18" s="21">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="21">
+        <v>742</v>
+      </c>
+      <c r="C19" s="21">
+        <v>841</v>
+      </c>
+      <c r="D19" s="21">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="21">
+        <v>71833</v>
+      </c>
+      <c r="C20" s="21">
+        <v>67573</v>
+      </c>
+      <c r="D20" s="21">
+        <v>139406</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="17"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="17"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>